--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484120_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484120_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5875</v>
+        <v>4.65</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1453</v>
+        <v>2.1049</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4422</v>
+        <v>2.5451</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7339</v>
+        <v>3.2338</v>
       </c>
       <c r="H2" t="n">
-        <v>1.899</v>
+        <v>1.8995</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8349</v>
+        <v>1.3344</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4445</v>
+        <v>1.6409</v>
       </c>
       <c r="K2" t="n">
-        <v>0.711</v>
+        <v>0.9932</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7335</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>2.2894</v>
+        <v>1.5929</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1881</v>
+        <v>0.9062</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1013</v>
+        <v>0.6867</v>
       </c>
       <c r="P2" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.9806</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.5441</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.4366</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1.9838</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.9838</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.5432</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-1.1846</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.6414</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.6032</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.8692</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-1.4724</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3836</v>
+        <v>4.1868</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8385</v>
+        <v>1.4741</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5451</v>
+        <v>2.7127</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2338</v>
+        <v>5.7339</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8995</v>
+        <v>1.899</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3344</v>
+        <v>3.8349</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6409</v>
+        <v>3.4445</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9932</v>
+        <v>0.711</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6477000000000001</v>
+        <v>2.7335</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5929</v>
+        <v>2.2894</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9062</v>
+        <v>1.1881</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6867</v>
+        <v>1.1013</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.247</v>
+        <v>-0.9439</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8105</v>
+        <v>-0.8558</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4366</v>
+        <v>-0.0881</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>-0.6032</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6986</v>
+        <v>3.4251</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9272</v>
+        <v>3.0746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7714</v>
+        <v>0.3506</v>
       </c>
       <c r="G4" t="n">
         <v>5.874</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2467</v>
+        <v>-0.5201</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6291</v>
+        <v>-0.4817</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3824</v>
+        <v>-0.0384</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1352</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1323</v>
+        <v>2.6614</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8398</v>
+        <v>-1.6754</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9721</v>
+        <v>4.3368</v>
       </c>
       <c r="G5" t="n">
         <v>3.4034</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7634</v>
+        <v>-1.2343</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8728</v>
+        <v>-0.7085</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.5258</v>
       </c>
       <c r="V5" t="n">
         <v>1.881</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8173</v>
+        <v>1.6475</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1471</v>
+        <v>-1.2888</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9644</v>
+        <v>2.9364</v>
       </c>
       <c r="G6" t="n">
         <v>3.6908</v>
@@ -922,13 +922,13 @@
         <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4099</v>
+        <v>-0.5796</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3173</v>
+        <v>-0.459</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0925</v>
+        <v>-0.1206</v>
       </c>
       <c r="V6" t="n">
         <v>0.1234</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9215</v>
+        <v>0.5183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5419</v>
+        <v>-0.244</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3797</v>
+        <v>0.7623</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0382</v>
+        <v>2.4412</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8971</v>
+        <v>0.2258</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9353</v>
+        <v>2.2154</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4685</v>
+        <v>2.1138</v>
       </c>
       <c r="K7" t="n">
-        <v>0.348</v>
+        <v>0.0605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>2.0533</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5068</v>
+        <v>0.3274</v>
       </c>
       <c r="N7" t="n">
-        <v>0.549</v>
+        <v>0.1653</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0558</v>
+        <v>0.162</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0906</v>
+        <v>-1.4468</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7993</v>
+        <v>-0.6914</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2913</v>
+        <v>-0.7554</v>
       </c>
       <c r="V7" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5079</v>
+        <v>0.0492</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7372</v>
+        <v>-0.2744</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2292</v>
+        <v>0.3235</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4412</v>
+        <v>-0.0382</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2258</v>
+        <v>0.8971</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2154</v>
+        <v>-0.9353</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1138</v>
+        <v>0.4685</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0605</v>
+        <v>0.348</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0533</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3274</v>
+        <v>-0.5068</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1653</v>
+        <v>0.549</v>
       </c>
       <c r="O8" t="n">
-        <v>0.162</v>
+        <v>-1.0558</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.473</v>
+        <v>0.2182</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1846</v>
+        <v>-0.017</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2884</v>
+        <v>0.2352</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1497</v>
+        <v>-0.5163</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8394</v>
+        <v>-1.3462</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6897</v>
+        <v>0.83</v>
       </c>
       <c r="G9" t="n">
         <v>2.827</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.0127</v>
+        <v>-2.3793</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5586</v>
+        <v>-1.0655</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4541</v>
+        <v>-1.3138</v>
       </c>
       <c r="V9" t="n">
         <v>1.615</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6293</v>
+        <v>-1.8044</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8049</v>
+        <v>-3.924</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1757</v>
+        <v>2.1195</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9849</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5929</v>
+        <v>-0.7681</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.255</v>
+        <v>-0.374</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3379</v>
+        <v>-0.394</v>
       </c>
       <c r="V10" t="n">
         <v>0.9405</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8831</v>
+        <v>-4.1998</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0438</v>
+        <v>-3.6131</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.5867</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8238</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5434</v>
+        <v>-0.8602</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8728</v>
+        <v>-0.4421</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6706</v>
+        <v>-0.4181</v>
       </c>
       <c r="V11" t="n">
         <v>0.0713</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.370799999999999</v>
+        <v>10.6178</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9593</v>
+        <v>-5.7123</v>
       </c>
       <c r="F12" t="n">
-        <v>16.3303</v>
+        <v>16.3302</v>
       </c>
       <c r="G12" t="n">
         <v>24.3572</v>
@@ -1366,7 +1366,7 @@
         <v>15.7554</v>
       </c>
       <c r="K12" t="n">
-        <v>1.894000000000001</v>
+        <v>1.894</v>
       </c>
       <c r="L12" t="n">
         <v>13.8615</v>
@@ -1381,7 +1381,7 @@
         <v>5.6365</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.935400000000001</v>
+        <v>-7.9354</v>
       </c>
       <c r="Q12" t="n">
         <v>-20.8301</v>
@@ -1390,13 +1390,13 @@
         <v>12.8951</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.7416</v>
+        <v>-9.494700000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.885999999999999</v>
+        <v>-5.6391</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.855599999999999</v>
+        <v>-3.8556</v>
       </c>
       <c r="V12" t="n">
         <v>3.6908</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5171</v>
+        <v>3.2562</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5685</v>
+        <v>1.8391</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9486</v>
+        <v>1.4171</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3955</v>
+        <v>-0.2799</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.634</v>
+        <v>1.0079</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2384</v>
+        <v>-1.2877</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4521</v>
+        <v>0.4285</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.311</v>
+        <v>1.0686</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7631</v>
+        <v>-0.64</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8477</v>
+        <v>-0.7084</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.323</v>
+        <v>-0.0607</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4365</v>
+        <v>0.7425</v>
       </c>
       <c r="T13" t="n">
-        <v>3.231</v>
+        <v>0.2041</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2055</v>
+        <v>0.5384</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5522</v>
+        <v>3.0604</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0229</v>
+        <v>1.1912</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5293</v>
+        <v>1.8692</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2799</v>
+        <v>-0.0132</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0079</v>
+        <v>2.5249</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2877</v>
+        <v>-2.5381</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4285</v>
+        <v>1.551</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0686</v>
+        <v>1.6989</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.64</v>
+        <v>-0.1479</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7084</v>
+        <v>-1.5642</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0607</v>
+        <v>0.826</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-2.3902</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5871</v>
+        <v>2.9758</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5871</v>
+        <v>2.9758</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0385</v>
+        <v>0.4351</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6121</v>
+        <v>-0.0225</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6506</v>
+        <v>0.4576</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2065</v>
+        <v>-0.3373</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2065</v>
+        <v>-0.3373</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9457</v>
+        <v>0.9639</v>
       </c>
       <c r="E15" t="n">
-        <v>0.273</v>
+        <v>0.3239</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6728</v>
+        <v>0.64</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0132</v>
+        <v>-0.3955</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5249</v>
+        <v>-0.634</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5381</v>
+        <v>0.2384</v>
       </c>
       <c r="J15" t="n">
-        <v>1.551</v>
+        <v>0.4521</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6989</v>
+        <v>-0.311</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1479</v>
+        <v>0.7631</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5642</v>
+        <v>-0.8477</v>
       </c>
       <c r="N15" t="n">
-        <v>0.826</v>
+        <v>-0.323</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3902</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9758</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9758</v>
+        <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6796</v>
+        <v>1.8833</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9408</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2612</v>
+        <v>0.8969</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3373</v>
+        <v>0.0713</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3373</v>
+        <v>0.8692</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.416</v>
+        <v>0.1446</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1849</v>
+        <v>-1.1463</v>
       </c>
       <c r="F16" t="n">
-        <v>1.231</v>
+        <v>1.2909</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1685</v>
+        <v>1.2636</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5429</v>
+        <v>2.4192</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6256</v>
+        <v>-1.1556</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3973</v>
+        <v>3.0933</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2855</v>
+        <v>2.0013</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6827</v>
+        <v>1.092</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5658</v>
+        <v>-1.8298</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2574</v>
+        <v>0.4179</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3084</v>
+        <v>-2.2477</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7935</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R16" t="n">
         <v>2.7774</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6719</v>
+        <v>1.0118</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7833</v>
+        <v>0.4026</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8887</v>
+        <v>0.6092</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.881</v>
+        <v>-0.9405</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.0118</v>
+        <v>-0.6745</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8692</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5185</v>
+        <v>-0.0197</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4362</v>
+        <v>-0.9464</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9548</v>
+        <v>0.9267</v>
       </c>
       <c r="G17" t="n">
         <v>-4.5698</v>
@@ -1780,13 +1780,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1839</v>
+        <v>2.6457</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0407</v>
+        <v>1.5306</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1432</v>
+        <v>1.1151</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6745</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9318</v>
+        <v>-0.4308</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1666</v>
+        <v>-1.5496</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2348</v>
+        <v>1.1188</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2636</v>
+        <v>-1.1685</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4192</v>
+        <v>-0.5429</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1556</v>
+        <v>-0.6256</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0933</v>
+        <v>0.3973</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0013</v>
+        <v>-0.2855</v>
       </c>
       <c r="L18" t="n">
-        <v>1.092</v>
+        <v>0.6827</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8298</v>
+        <v>-1.5658</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4179</v>
+        <v>-0.2574</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2477</v>
+        <v>-1.3084</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
         <v>2.7774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0646</v>
+        <v>1.8252</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6177</v>
+        <v>1.0488</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5531</v>
+        <v>0.7764</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>-1.881</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6745</v>
+        <v>-1.0118</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3532</v>
+        <v>-0.9528</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2604</v>
+        <v>-2.0563</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9072</v>
+        <v>1.1036</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3462</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1877</v>
+        <v>0.5881</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2436</v>
+        <v>-0.0396</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4313</v>
+        <v>0.6277</v>
       </c>
       <c r="V19" t="n">
         <v>0.4085</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.975</v>
+        <v>-1.6689</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0147</v>
+        <v>-1.7086</v>
       </c>
       <c r="F20" t="n">
         <v>0.0397</v>
@@ -2014,10 +2014,10 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0737</v>
+        <v>0.3798</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3627</v>
+        <v>-0.0566</v>
       </c>
       <c r="U20" t="n">
         <v>0.4364</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6886</v>
+        <v>-2.8085</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9254</v>
+        <v>-2.1294</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7632</v>
+        <v>-0.6791</v>
       </c>
       <c r="G21" t="n">
         <v>-3.51</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2262</v>
+        <v>0.1063</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0056</v>
+        <v>-0.2097</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2318</v>
+        <v>0.316</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0878</v>
+        <v>-4.394</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8889</v>
+        <v>-3.9706</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1989</v>
+        <v>-0.4234</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9107</v>
@@ -2170,13 +2170,13 @@
         <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.161</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1109</v>
+        <v>-0.1926</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9499</v>
+        <v>0.7254</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.284</v>
+        <v>-6.5214</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6874</v>
+        <v>-6.1772</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5967</v>
+        <v>-0.3442</v>
       </c>
       <c r="G23" t="n">
         <v>-6.9735</v>
@@ -2248,13 +2248,13 @@
         <v>2.1822</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1717</v>
+        <v>0.591</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.306</v>
+        <v>0.2042</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1343</v>
+        <v>0.3868</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3373</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.370899999999999</v>
+        <v>-9.371</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.3303</v>
+        <v>-16.3302</v>
       </c>
       <c r="F24" t="n">
-        <v>6.9594</v>
+        <v>6.959300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-24.3572</v>
@@ -2326,16 +2326,16 @@
         <v>20.8305</v>
       </c>
       <c r="S24" t="n">
-        <v>10.7415</v>
+        <v>10.7416</v>
       </c>
       <c r="T24" t="n">
-        <v>3.8556</v>
+        <v>3.8557</v>
       </c>
       <c r="U24" t="n">
-        <v>6.885999999999999</v>
+        <v>6.8859</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.6908</v>
+        <v>-3.690799999999999</v>
       </c>
       <c r="W24" t="n">
         <v>1.3107</v>
